--- a/docs/reports/WR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
+++ b/docs/reports/WR_Kavach_Unified_KPI_Jun22-Jun28.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,6 +309,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -714,7 +732,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -857,19 +874,19 @@
         <f>'Daily Breakdown'!J300</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="46">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="47">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="48">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="47">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -877,19 +894,19 @@
         <f>'Daily Breakdown'!K300</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="46">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="47">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="47">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="48">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -939,7 +956,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1011,7 +1034,7 @@
       <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1051,7 +1074,7 @@
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1091,7 +1114,7 @@
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1131,7 +1154,7 @@
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1171,7 +1194,7 @@
       <c r="C8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1211,7 +1234,7 @@
       <c r="C9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1251,7 +1274,7 @@
       <c r="C10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1291,7 +1314,7 @@
       <c r="C11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1331,7 +1354,7 @@
       <c r="C12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1371,7 +1394,7 @@
       <c r="C13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1411,7 +1434,7 @@
       <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1451,7 +1474,7 @@
       <c r="C15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1491,7 +1514,7 @@
       <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1531,7 +1554,7 @@
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1571,7 +1594,7 @@
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1611,7 +1634,7 @@
       <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1651,7 +1674,7 @@
       <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1691,7 +1714,7 @@
       <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1731,7 +1754,7 @@
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1771,7 +1794,7 @@
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1811,7 +1834,7 @@
       <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="49" t="n">
         <v>36.49</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1851,7 +1874,7 @@
       <c r="C25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="49" t="n">
         <v>43.21</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1891,7 +1914,7 @@
       <c r="C26" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="49" t="n">
         <v>85.41</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1931,7 +1954,7 @@
       <c r="C27" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="49" t="n">
         <v>55.63</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1971,7 +1994,7 @@
       <c r="C28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="49" t="n">
         <v>64.67</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2011,7 +2034,7 @@
       <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="49" t="n">
         <v>40.37</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2051,7 +2074,7 @@
       <c r="C30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="49" t="n">
         <v>36.96</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2091,7 +2114,7 @@
       <c r="C31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="49" t="n">
         <v>56.83</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2131,7 +2154,7 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="49" t="n">
         <v>50.68</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2171,7 +2194,7 @@
       <c r="C33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="49" t="n">
         <v>38.17</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2211,7 +2234,7 @@
       <c r="C34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="49" t="n">
         <v>36.84</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2251,7 +2274,7 @@
       <c r="C35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="49" t="n">
         <v>39.48</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2291,7 +2314,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="49" t="n">
         <v>52.14</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2331,7 +2354,7 @@
       <c r="C37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="49" t="n">
         <v>38.25</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2371,7 +2394,7 @@
       <c r="C38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="49" t="n">
         <v>40.15</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2411,7 +2434,7 @@
       <c r="C39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="49" t="n">
         <v>38.53</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2451,7 +2474,7 @@
       <c r="C40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="49" t="n">
         <v>40.26</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2491,7 +2514,7 @@
       <c r="C41" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="49" t="n">
         <v>36.73</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2531,7 +2554,7 @@
       <c r="C42" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="49" t="n">
         <v>1.99</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2571,7 +2594,7 @@
       <c r="C43" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="49" t="n">
         <v>36.25</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2611,7 +2634,7 @@
       <c r="C44" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="49" t="n">
         <v>54.76</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2651,7 +2674,7 @@
       <c r="C45" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="49" t="n">
         <v>35.76</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2692,7 +2715,7 @@
         <f>SUM(C4:C45)</f>
         <v/>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="50">
         <f>SUM(D4:D45)</f>
         <v/>
       </c>
@@ -2701,7 +2724,7 @@
         <v/>
       </c>
       <c r="F46" s="23">
-        <f>SUM(F4:F45)</f>
+        <f>SUMIF(E4:E45,"&gt;0",F4:F45)</f>
         <v/>
       </c>
       <c r="G46" s="24">
@@ -2739,7 +2762,7 @@
       <c r="C47" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2779,7 +2802,7 @@
       <c r="C48" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E48" s="18" t="n">
@@ -2819,7 +2842,7 @@
       <c r="C49" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E49" s="18" t="n">
@@ -2859,7 +2882,7 @@
       <c r="C50" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E50" s="18" t="n">
@@ -2899,7 +2922,7 @@
       <c r="C51" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E51" s="18" t="n">
@@ -2939,7 +2962,7 @@
       <c r="C52" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E52" s="18" t="n">
@@ -2979,7 +3002,7 @@
       <c r="C53" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="49" t="n">
         <v>93.86</v>
       </c>
       <c r="E53" s="18" t="n">
@@ -3019,7 +3042,7 @@
       <c r="C54" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E54" s="18" t="n">
@@ -3059,7 +3082,7 @@
       <c r="C55" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E55" s="18" t="n">
@@ -3099,7 +3122,7 @@
       <c r="C56" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E56" s="18" t="n">
@@ -3139,7 +3162,7 @@
       <c r="C57" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="49" t="n">
         <v>93.83</v>
       </c>
       <c r="E57" s="18" t="n">
@@ -3179,7 +3202,7 @@
       <c r="C58" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E58" s="18" t="n">
@@ -3219,7 +3242,7 @@
       <c r="C59" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="17" t="n">
+      <c r="D59" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E59" s="18" t="n">
@@ -3259,7 +3282,7 @@
       <c r="C60" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="49" t="n">
         <v>93.86</v>
       </c>
       <c r="E60" s="18" t="n">
@@ -3299,7 +3322,7 @@
       <c r="C61" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E61" s="18" t="n">
@@ -3339,7 +3362,7 @@
       <c r="C62" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E62" s="18" t="n">
@@ -3379,7 +3402,7 @@
       <c r="C63" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E63" s="18" t="n">
@@ -3419,7 +3442,7 @@
       <c r="C64" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E64" s="18" t="n">
@@ -3459,7 +3482,7 @@
       <c r="C65" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="17" t="n">
+      <c r="D65" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E65" s="18" t="n">
@@ -3499,7 +3522,7 @@
       <c r="C66" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E66" s="18" t="n">
@@ -3539,7 +3562,7 @@
       <c r="C67" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="17" t="n">
+      <c r="D67" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E67" s="18" t="n">
@@ -3579,7 +3602,7 @@
       <c r="C68" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D68" s="17" t="n">
+      <c r="D68" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E68" s="18" t="n">
@@ -3619,7 +3642,7 @@
       <c r="C69" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E69" s="18" t="n">
@@ -3659,7 +3682,7 @@
       <c r="C70" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="49" t="n">
         <v>92.20999999999999</v>
       </c>
       <c r="E70" s="18" t="n">
@@ -3699,7 +3722,7 @@
       <c r="C71" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E71" s="18" t="n">
@@ -3739,7 +3762,7 @@
       <c r="C72" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E72" s="18" t="n">
@@ -3779,7 +3802,7 @@
       <c r="C73" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E73" s="18" t="n">
@@ -3819,7 +3842,7 @@
       <c r="C74" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D74" s="17" t="n">
+      <c r="D74" s="49" t="n">
         <v>38.53</v>
       </c>
       <c r="E74" s="18" t="n">
@@ -3859,7 +3882,7 @@
       <c r="C75" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="49" t="n">
         <v>53.33</v>
       </c>
       <c r="E75" s="18" t="n">
@@ -3899,7 +3922,7 @@
       <c r="C76" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D76" s="17" t="n">
+      <c r="D76" s="49" t="n">
         <v>50.03</v>
       </c>
       <c r="E76" s="18" t="n">
@@ -3939,7 +3962,7 @@
       <c r="C77" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="17" t="n">
+      <c r="D77" s="49" t="n">
         <v>53.28</v>
       </c>
       <c r="E77" s="18" t="n">
@@ -3979,7 +4002,7 @@
       <c r="C78" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="17" t="n">
+      <c r="D78" s="49" t="n">
         <v>37.09</v>
       </c>
       <c r="E78" s="18" t="n">
@@ -4019,7 +4042,7 @@
       <c r="C79" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D79" s="49" t="n">
         <v>36.53</v>
       </c>
       <c r="E79" s="18" t="n">
@@ -4059,7 +4082,7 @@
       <c r="C80" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D80" s="17" t="n">
+      <c r="D80" s="49" t="n">
         <v>40.53</v>
       </c>
       <c r="E80" s="18" t="n">
@@ -4099,7 +4122,7 @@
       <c r="C81" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="17" t="n">
+      <c r="D81" s="49" t="n">
         <v>36.88</v>
       </c>
       <c r="E81" s="18" t="n">
@@ -4139,7 +4162,7 @@
       <c r="C82" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="17" t="n">
+      <c r="D82" s="49" t="n">
         <v>38.81</v>
       </c>
       <c r="E82" s="18" t="n">
@@ -4179,7 +4202,7 @@
       <c r="C83" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="17" t="n">
+      <c r="D83" s="49" t="n">
         <v>36.43</v>
       </c>
       <c r="E83" s="18" t="n">
@@ -4219,7 +4242,7 @@
       <c r="C84" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D84" s="17" t="n">
+      <c r="D84" s="49" t="n">
         <v>36.9</v>
       </c>
       <c r="E84" s="18" t="n">
@@ -4259,7 +4282,7 @@
       <c r="C85" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="D85" s="49" t="n">
         <v>36.96</v>
       </c>
       <c r="E85" s="18" t="n">
@@ -4299,7 +4322,7 @@
       <c r="C86" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="17" t="n">
+      <c r="D86" s="49" t="n">
         <v>36.84</v>
       </c>
       <c r="E86" s="18" t="n">
@@ -4339,7 +4362,7 @@
       <c r="C87" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D87" s="17" t="n">
+      <c r="D87" s="49" t="n">
         <v>36.85</v>
       </c>
       <c r="E87" s="18" t="n">
@@ -4379,7 +4402,7 @@
       <c r="C88" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="17" t="n">
+      <c r="D88" s="49" t="n">
         <v>34.97</v>
       </c>
       <c r="E88" s="18" t="n">
@@ -4419,7 +4442,7 @@
       <c r="C89" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="17" t="n">
+      <c r="D89" s="49" t="n">
         <v>27.25</v>
       </c>
       <c r="E89" s="18" t="n">
@@ -4459,7 +4482,7 @@
       <c r="C90" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D90" s="17" t="n">
+      <c r="D90" s="49" t="n">
         <v>1.98</v>
       </c>
       <c r="E90" s="18" t="n">
@@ -4500,7 +4523,7 @@
         <f>SUM(C47:C90)</f>
         <v/>
       </c>
-      <c r="D91" s="22">
+      <c r="D91" s="50">
         <f>SUM(D47:D90)</f>
         <v/>
       </c>
@@ -4509,7 +4532,7 @@
         <v/>
       </c>
       <c r="F91" s="23">
-        <f>SUM(F47:F90)</f>
+        <f>SUMIF(E47:E90,"&gt;0",F47:F90)</f>
         <v/>
       </c>
       <c r="G91" s="24">
@@ -4547,7 +4570,7 @@
       <c r="C92" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="D92" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E92" s="18" t="n">
@@ -4587,7 +4610,7 @@
       <c r="C93" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E93" s="18" t="n">
@@ -4627,7 +4650,7 @@
       <c r="C94" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D94" s="17" t="n">
+      <c r="D94" s="49" t="n">
         <v>91.72</v>
       </c>
       <c r="E94" s="18" t="n">
@@ -4667,7 +4690,7 @@
       <c r="C95" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D95" s="17" t="n">
+      <c r="D95" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E95" s="18" t="n">
@@ -4707,7 +4730,7 @@
       <c r="C96" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D96" s="17" t="n">
+      <c r="D96" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E96" s="18" t="n">
@@ -4747,7 +4770,7 @@
       <c r="C97" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D97" s="17" t="n">
+      <c r="D97" s="49" t="n">
         <v>90.89</v>
       </c>
       <c r="E97" s="18" t="n">
@@ -4787,7 +4810,7 @@
       <c r="C98" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D98" s="17" t="n">
+      <c r="D98" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E98" s="18" t="n">
@@ -4827,7 +4850,7 @@
       <c r="C99" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D99" s="17" t="n">
+      <c r="D99" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E99" s="18" t="n">
@@ -4867,7 +4890,7 @@
       <c r="C100" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D100" s="17" t="n">
+      <c r="D100" s="49" t="n">
         <v>93.31</v>
       </c>
       <c r="E100" s="18" t="n">
@@ -4907,7 +4930,7 @@
       <c r="C101" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D101" s="17" t="n">
+      <c r="D101" s="49" t="n">
         <v>93.31</v>
       </c>
       <c r="E101" s="18" t="n">
@@ -4947,7 +4970,7 @@
       <c r="C102" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D102" s="17" t="n">
+      <c r="D102" s="49" t="n">
         <v>93.84</v>
       </c>
       <c r="E102" s="18" t="n">
@@ -4987,7 +5010,7 @@
       <c r="C103" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D103" s="17" t="n">
+      <c r="D103" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E103" s="18" t="n">
@@ -5027,7 +5050,7 @@
       <c r="C104" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D104" s="17" t="n">
+      <c r="D104" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E104" s="18" t="n">
@@ -5067,7 +5090,7 @@
       <c r="C105" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D105" s="17" t="n">
+      <c r="D105" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E105" s="18" t="n">
@@ -5107,7 +5130,7 @@
       <c r="C106" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D106" s="17" t="n">
+      <c r="D106" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E106" s="18" t="n">
@@ -5147,7 +5170,7 @@
       <c r="C107" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D107" s="17" t="n">
+      <c r="D107" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E107" s="18" t="n">
@@ -5187,7 +5210,7 @@
       <c r="C108" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D108" s="17" t="n">
+      <c r="D108" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E108" s="18" t="n">
@@ -5227,7 +5250,7 @@
       <c r="C109" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D109" s="17" t="n">
+      <c r="D109" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E109" s="18" t="n">
@@ -5267,7 +5290,7 @@
       <c r="C110" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D110" s="17" t="n">
+      <c r="D110" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E110" s="18" t="n">
@@ -5307,7 +5330,7 @@
       <c r="C111" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D111" s="17" t="n">
+      <c r="D111" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E111" s="18" t="n">
@@ -5347,7 +5370,7 @@
       <c r="C112" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="17" t="n">
+      <c r="D112" s="49" t="n">
         <v>36.72</v>
       </c>
       <c r="E112" s="18" t="n">
@@ -5387,7 +5410,7 @@
       <c r="C113" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="17" t="n">
+      <c r="D113" s="49" t="n">
         <v>54.5</v>
       </c>
       <c r="E113" s="18" t="n">
@@ -5427,7 +5450,7 @@
       <c r="C114" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="17" t="n">
+      <c r="D114" s="49" t="n">
         <v>53.96</v>
       </c>
       <c r="E114" s="18" t="n">
@@ -5467,7 +5490,7 @@
       <c r="C115" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="17" t="n">
+      <c r="D115" s="49" t="n">
         <v>52.5</v>
       </c>
       <c r="E115" s="18" t="n">
@@ -5507,7 +5530,7 @@
       <c r="C116" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="17" t="n">
+      <c r="D116" s="49" t="n">
         <v>61.75</v>
       </c>
       <c r="E116" s="18" t="n">
@@ -5547,7 +5570,7 @@
       <c r="C117" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="17" t="n">
+      <c r="D117" s="49" t="n">
         <v>36.8</v>
       </c>
       <c r="E117" s="18" t="n">
@@ -5587,7 +5610,7 @@
       <c r="C118" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="17" t="n">
+      <c r="D118" s="49" t="n">
         <v>32.27</v>
       </c>
       <c r="E118" s="18" t="n">
@@ -5627,7 +5650,7 @@
       <c r="C119" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="17" t="n">
+      <c r="D119" s="49" t="n">
         <v>40.4</v>
       </c>
       <c r="E119" s="18" t="n">
@@ -5667,7 +5690,7 @@
       <c r="C120" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="17" t="n">
+      <c r="D120" s="49" t="n">
         <v>51.9</v>
       </c>
       <c r="E120" s="18" t="n">
@@ -5707,7 +5730,7 @@
       <c r="C121" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="17" t="n">
+      <c r="D121" s="49" t="n">
         <v>51.95</v>
       </c>
       <c r="E121" s="18" t="n">
@@ -5747,7 +5770,7 @@
       <c r="C122" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="17" t="n">
+      <c r="D122" s="49" t="n">
         <v>38.39</v>
       </c>
       <c r="E122" s="18" t="n">
@@ -5787,7 +5810,7 @@
       <c r="C123" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="17" t="n">
+      <c r="D123" s="49" t="n">
         <v>38.49</v>
       </c>
       <c r="E123" s="18" t="n">
@@ -5827,7 +5850,7 @@
       <c r="C124" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="17" t="n">
+      <c r="D124" s="49" t="n">
         <v>36.97</v>
       </c>
       <c r="E124" s="18" t="n">
@@ -5867,7 +5890,7 @@
       <c r="C125" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="17" t="n">
+      <c r="D125" s="49" t="n">
         <v>6.57</v>
       </c>
       <c r="E125" s="18" t="n">
@@ -5907,7 +5930,7 @@
       <c r="C126" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="17" t="n">
+      <c r="D126" s="49" t="n">
         <v>32.46</v>
       </c>
       <c r="E126" s="18" t="n">
@@ -5947,7 +5970,7 @@
       <c r="C127" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D127" s="17" t="n">
+      <c r="D127" s="49" t="n">
         <v>1.98</v>
       </c>
       <c r="E127" s="18" t="n">
@@ -5987,7 +6010,7 @@
       <c r="C128" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="17" t="n">
+      <c r="D128" s="49" t="n">
         <v>15.03</v>
       </c>
       <c r="E128" s="18" t="n">
@@ -6027,7 +6050,7 @@
       <c r="C129" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D129" s="17" t="n">
+      <c r="D129" s="49" t="n">
         <v>30.97</v>
       </c>
       <c r="E129" s="18" t="n">
@@ -6068,7 +6091,7 @@
         <f>SUM(C92:C129)</f>
         <v/>
       </c>
-      <c r="D130" s="22">
+      <c r="D130" s="50">
         <f>SUM(D92:D129)</f>
         <v/>
       </c>
@@ -6077,7 +6100,7 @@
         <v/>
       </c>
       <c r="F130" s="23">
-        <f>SUM(F92:F129)</f>
+        <f>SUMIF(E92:E129,"&gt;0",F92:F129)</f>
         <v/>
       </c>
       <c r="G130" s="24">
@@ -6115,7 +6138,7 @@
       <c r="C131" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D131" s="17" t="n">
+      <c r="D131" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E131" s="18" t="n">
@@ -6155,7 +6178,7 @@
       <c r="C132" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D132" s="17" t="n">
+      <c r="D132" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E132" s="18" t="n">
@@ -6195,7 +6218,7 @@
       <c r="C133" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D133" s="17" t="n">
+      <c r="D133" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E133" s="18" t="n">
@@ -6235,7 +6258,7 @@
       <c r="C134" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D134" s="17" t="n">
+      <c r="D134" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E134" s="18" t="n">
@@ -6275,7 +6298,7 @@
       <c r="C135" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D135" s="17" t="n">
+      <c r="D135" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E135" s="18" t="n">
@@ -6315,7 +6338,7 @@
       <c r="C136" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D136" s="17" t="n">
+      <c r="D136" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E136" s="18" t="n">
@@ -6355,7 +6378,7 @@
       <c r="C137" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="17" t="n">
+      <c r="D137" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E137" s="18" t="n">
@@ -6395,7 +6418,7 @@
       <c r="C138" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D138" s="17" t="n">
+      <c r="D138" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E138" s="18" t="n">
@@ -6435,7 +6458,7 @@
       <c r="C139" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D139" s="17" t="n">
+      <c r="D139" s="49" t="n">
         <v>93.33</v>
       </c>
       <c r="E139" s="18" t="n">
@@ -6475,7 +6498,7 @@
       <c r="C140" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D140" s="17" t="n">
+      <c r="D140" s="49" t="n">
         <v>91.72</v>
       </c>
       <c r="E140" s="18" t="n">
@@ -6515,7 +6538,7 @@
       <c r="C141" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D141" s="17" t="n">
+      <c r="D141" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E141" s="18" t="n">
@@ -6555,7 +6578,7 @@
       <c r="C142" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D142" s="17" t="n">
+      <c r="D142" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E142" s="18" t="n">
@@ -6595,7 +6618,7 @@
       <c r="C143" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D143" s="17" t="n">
+      <c r="D143" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E143" s="18" t="n">
@@ -6635,7 +6658,7 @@
       <c r="C144" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D144" s="17" t="n">
+      <c r="D144" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E144" s="18" t="n">
@@ -6675,7 +6698,7 @@
       <c r="C145" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D145" s="17" t="n">
+      <c r="D145" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E145" s="18" t="n">
@@ -6715,7 +6738,7 @@
       <c r="C146" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D146" s="17" t="n">
+      <c r="D146" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E146" s="18" t="n">
@@ -6755,7 +6778,7 @@
       <c r="C147" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D147" s="17" t="n">
+      <c r="D147" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E147" s="18" t="n">
@@ -6795,7 +6818,7 @@
       <c r="C148" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D148" s="17" t="n">
+      <c r="D148" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E148" s="18" t="n">
@@ -6835,7 +6858,7 @@
       <c r="C149" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D149" s="17" t="n">
+      <c r="D149" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E149" s="18" t="n">
@@ -6875,7 +6898,7 @@
       <c r="C150" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D150" s="17" t="n">
+      <c r="D150" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E150" s="18" t="n">
@@ -6915,7 +6938,7 @@
       <c r="C151" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D151" s="17" t="n">
+      <c r="D151" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E151" s="18" t="n">
@@ -6955,7 +6978,7 @@
       <c r="C152" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D152" s="17" t="n">
+      <c r="D152" s="49" t="n">
         <v>36.44</v>
       </c>
       <c r="E152" s="18" t="n">
@@ -6995,7 +7018,7 @@
       <c r="C153" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D153" s="17" t="n">
+      <c r="D153" s="49" t="n">
         <v>66.65000000000001</v>
       </c>
       <c r="E153" s="18" t="n">
@@ -7035,7 +7058,7 @@
       <c r="C154" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D154" s="17" t="n">
+      <c r="D154" s="49" t="n">
         <v>87.3</v>
       </c>
       <c r="E154" s="18" t="n">
@@ -7075,7 +7098,7 @@
       <c r="C155" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D155" s="17" t="n">
+      <c r="D155" s="49" t="n">
         <v>40.48</v>
       </c>
       <c r="E155" s="18" t="n">
@@ -7115,7 +7138,7 @@
       <c r="C156" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D156" s="17" t="n">
+      <c r="D156" s="49" t="n">
         <v>48.76</v>
       </c>
       <c r="E156" s="18" t="n">
@@ -7155,7 +7178,7 @@
       <c r="C157" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D157" s="17" t="n">
+      <c r="D157" s="49" t="n">
         <v>44.66</v>
       </c>
       <c r="E157" s="18" t="n">
@@ -7195,7 +7218,7 @@
       <c r="C158" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D158" s="17" t="n">
+      <c r="D158" s="49" t="n">
         <v>54.35</v>
       </c>
       <c r="E158" s="18" t="n">
@@ -7235,7 +7258,7 @@
       <c r="C159" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D159" s="17" t="n">
+      <c r="D159" s="49" t="n">
         <v>41.7</v>
       </c>
       <c r="E159" s="18" t="n">
@@ -7275,7 +7298,7 @@
       <c r="C160" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D160" s="17" t="n">
+      <c r="D160" s="49" t="n">
         <v>38.37</v>
       </c>
       <c r="E160" s="18" t="n">
@@ -7315,7 +7338,7 @@
       <c r="C161" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D161" s="17" t="n">
+      <c r="D161" s="49" t="n">
         <v>38.28</v>
       </c>
       <c r="E161" s="18" t="n">
@@ -7355,7 +7378,7 @@
       <c r="C162" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D162" s="17" t="n">
+      <c r="D162" s="49" t="n">
         <v>36.98</v>
       </c>
       <c r="E162" s="18" t="n">
@@ -7395,7 +7418,7 @@
       <c r="C163" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D163" s="17" t="n">
+      <c r="D163" s="49" t="n">
         <v>36.74</v>
       </c>
       <c r="E163" s="18" t="n">
@@ -7435,7 +7458,7 @@
       <c r="C164" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D164" s="17" t="n">
+      <c r="D164" s="49" t="n">
         <v>16.11</v>
       </c>
       <c r="E164" s="18" t="n">
@@ -7475,7 +7498,7 @@
       <c r="C165" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D165" s="17" t="n">
+      <c r="D165" s="49" t="n">
         <v>36.26</v>
       </c>
       <c r="E165" s="18" t="n">
@@ -7515,7 +7538,7 @@
       <c r="C166" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D166" s="17" t="n">
+      <c r="D166" s="49" t="n">
         <v>1.98</v>
       </c>
       <c r="E166" s="18" t="n">
@@ -7555,7 +7578,7 @@
       <c r="C167" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D167" s="17" t="n">
+      <c r="D167" s="49" t="n">
         <v>30.32</v>
       </c>
       <c r="E167" s="18" t="n">
@@ -7596,7 +7619,7 @@
         <f>SUM(C131:C167)</f>
         <v/>
       </c>
-      <c r="D168" s="22">
+      <c r="D168" s="50">
         <f>SUM(D131:D167)</f>
         <v/>
       </c>
@@ -7605,7 +7628,7 @@
         <v/>
       </c>
       <c r="F168" s="23">
-        <f>SUM(F131:F167)</f>
+        <f>SUMIF(E131:E167,"&gt;0",F131:F167)</f>
         <v/>
       </c>
       <c r="G168" s="24">
@@ -7643,7 +7666,7 @@
       <c r="C169" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D169" s="17" t="n">
+      <c r="D169" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E169" s="18" t="n">
@@ -7683,7 +7706,7 @@
       <c r="C170" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D170" s="17" t="n">
+      <c r="D170" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E170" s="18" t="n">
@@ -7723,7 +7746,7 @@
       <c r="C171" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D171" s="17" t="n">
+      <c r="D171" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E171" s="18" t="n">
@@ -7763,7 +7786,7 @@
       <c r="C172" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D172" s="17" t="n">
+      <c r="D172" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E172" s="18" t="n">
@@ -7803,7 +7826,7 @@
       <c r="C173" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D173" s="17" t="n">
+      <c r="D173" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E173" s="18" t="n">
@@ -7843,7 +7866,7 @@
       <c r="C174" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D174" s="17" t="n">
+      <c r="D174" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E174" s="18" t="n">
@@ -7883,7 +7906,7 @@
       <c r="C175" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D175" s="17" t="n">
+      <c r="D175" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E175" s="18" t="n">
@@ -7923,7 +7946,7 @@
       <c r="C176" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D176" s="17" t="n">
+      <c r="D176" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E176" s="18" t="n">
@@ -7963,7 +7986,7 @@
       <c r="C177" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D177" s="17" t="n">
+      <c r="D177" s="49" t="n">
         <v>93.31</v>
       </c>
       <c r="E177" s="18" t="n">
@@ -8003,7 +8026,7 @@
       <c r="C178" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D178" s="17" t="n">
+      <c r="D178" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E178" s="18" t="n">
@@ -8043,7 +8066,7 @@
       <c r="C179" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D179" s="17" t="n">
+      <c r="D179" s="49" t="n">
         <v>90.89</v>
       </c>
       <c r="E179" s="18" t="n">
@@ -8083,7 +8106,7 @@
       <c r="C180" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D180" s="17" t="n">
+      <c r="D180" s="49" t="n">
         <v>93.31</v>
       </c>
       <c r="E180" s="18" t="n">
@@ -8123,7 +8146,7 @@
       <c r="C181" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D181" s="17" t="n">
+      <c r="D181" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E181" s="18" t="n">
@@ -8163,7 +8186,7 @@
       <c r="C182" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D182" s="17" t="n">
+      <c r="D182" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E182" s="18" t="n">
@@ -8203,7 +8226,7 @@
       <c r="C183" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D183" s="17" t="n">
+      <c r="D183" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E183" s="18" t="n">
@@ -8243,7 +8266,7 @@
       <c r="C184" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D184" s="17" t="n">
+      <c r="D184" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E184" s="18" t="n">
@@ -8283,7 +8306,7 @@
       <c r="C185" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D185" s="17" t="n">
+      <c r="D185" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E185" s="18" t="n">
@@ -8323,7 +8346,7 @@
       <c r="C186" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D186" s="17" t="n">
+      <c r="D186" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E186" s="18" t="n">
@@ -8363,7 +8386,7 @@
       <c r="C187" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D187" s="17" t="n">
+      <c r="D187" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E187" s="18" t="n">
@@ -8403,7 +8426,7 @@
       <c r="C188" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D188" s="17" t="n">
+      <c r="D188" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E188" s="18" t="n">
@@ -8443,7 +8466,7 @@
       <c r="C189" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D189" s="17" t="n">
+      <c r="D189" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E189" s="18" t="n">
@@ -8483,7 +8506,7 @@
       <c r="C190" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D190" s="17" t="n">
+      <c r="D190" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E190" s="18" t="n">
@@ -8523,7 +8546,7 @@
       <c r="C191" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D191" s="17" t="n">
+      <c r="D191" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E191" s="18" t="n">
@@ -8563,7 +8586,7 @@
       <c r="C192" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D192" s="17" t="n">
+      <c r="D192" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E192" s="18" t="n">
@@ -8603,7 +8626,7 @@
       <c r="C193" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D193" s="17" t="n">
+      <c r="D193" s="49" t="n">
         <v>91.70999999999999</v>
       </c>
       <c r="E193" s="18" t="n">
@@ -8643,7 +8666,7 @@
       <c r="C194" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D194" s="17" t="n">
+      <c r="D194" s="49" t="n">
         <v>93.86</v>
       </c>
       <c r="E194" s="18" t="n">
@@ -8683,7 +8706,7 @@
       <c r="C195" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D195" s="17" t="n">
+      <c r="D195" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E195" s="18" t="n">
@@ -8723,7 +8746,7 @@
       <c r="C196" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D196" s="17" t="n">
+      <c r="D196" s="49" t="n">
         <v>93.31</v>
       </c>
       <c r="E196" s="18" t="n">
@@ -8763,7 +8786,7 @@
       <c r="C197" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D197" s="17" t="n">
+      <c r="D197" s="49" t="n">
         <v>92.14</v>
       </c>
       <c r="E197" s="18" t="n">
@@ -8803,7 +8826,7 @@
       <c r="C198" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D198" s="17" t="n">
+      <c r="D198" s="49" t="n">
         <v>92.93000000000001</v>
       </c>
       <c r="E198" s="18" t="n">
@@ -8843,7 +8866,7 @@
       <c r="C199" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D199" s="17" t="n">
+      <c r="D199" s="49" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="E199" s="18" t="n">
@@ -8883,7 +8906,7 @@
       <c r="C200" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D200" s="17" t="n">
+      <c r="D200" s="49" t="n">
         <v>36.39</v>
       </c>
       <c r="E200" s="18" t="n">
@@ -8923,7 +8946,7 @@
       <c r="C201" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D201" s="17" t="n">
+      <c r="D201" s="49" t="n">
         <v>77.18000000000001</v>
       </c>
       <c r="E201" s="18" t="n">
@@ -8963,7 +8986,7 @@
       <c r="C202" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D202" s="17" t="n">
+      <c r="D202" s="49" t="n">
         <v>52.21</v>
       </c>
       <c r="E202" s="18" t="n">
@@ -9003,7 +9026,7 @@
       <c r="C203" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D203" s="17" t="n">
+      <c r="D203" s="49" t="n">
         <v>67.5</v>
       </c>
       <c r="E203" s="18" t="n">
@@ -9043,7 +9066,7 @@
       <c r="C204" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D204" s="17" t="n">
+      <c r="D204" s="49" t="n">
         <v>75.31999999999999</v>
       </c>
       <c r="E204" s="18" t="n">
@@ -9083,7 +9106,7 @@
       <c r="C205" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D205" s="17" t="n">
+      <c r="D205" s="49" t="n">
         <v>41.4</v>
       </c>
       <c r="E205" s="18" t="n">
@@ -9123,7 +9146,7 @@
       <c r="C206" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D206" s="17" t="n">
+      <c r="D206" s="49" t="n">
         <v>40.29</v>
       </c>
       <c r="E206" s="18" t="n">
@@ -9163,7 +9186,7 @@
       <c r="C207" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D207" s="17" t="n">
+      <c r="D207" s="49" t="n">
         <v>36.86</v>
       </c>
       <c r="E207" s="18" t="n">
@@ -9203,7 +9226,7 @@
       <c r="C208" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D208" s="17" t="n">
+      <c r="D208" s="49" t="n">
         <v>51.95</v>
       </c>
       <c r="E208" s="18" t="n">
@@ -9243,7 +9266,7 @@
       <c r="C209" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D209" s="17" t="n">
+      <c r="D209" s="49" t="n">
         <v>51.45</v>
       </c>
       <c r="E209" s="18" t="n">
@@ -9283,7 +9306,7 @@
       <c r="C210" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D210" s="17" t="n">
+      <c r="D210" s="49" t="n">
         <v>36.87</v>
       </c>
       <c r="E210" s="18" t="n">
@@ -9323,7 +9346,7 @@
       <c r="C211" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D211" s="17" t="n">
+      <c r="D211" s="49" t="n">
         <v>28.81</v>
       </c>
       <c r="E211" s="18" t="n">
@@ -9363,7 +9386,7 @@
       <c r="C212" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D212" s="17" t="n">
+      <c r="D212" s="49" t="n">
         <v>36.86</v>
       </c>
       <c r="E212" s="18" t="n">
@@ -9403,7 +9426,7 @@
       <c r="C213" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D213" s="17" t="n">
+      <c r="D213" s="49" t="n">
         <v>1.98</v>
       </c>
       <c r="E213" s="18" t="n">
@@ -9444,7 +9467,7 @@
         <f>SUM(C169:C213)</f>
         <v/>
       </c>
-      <c r="D214" s="22">
+      <c r="D214" s="50">
         <f>SUM(D169:D213)</f>
         <v/>
       </c>
@@ -9453,7 +9476,7 @@
         <v/>
       </c>
       <c r="F214" s="23">
-        <f>SUM(F169:F213)</f>
+        <f>SUMIF(E169:E213,"&gt;0",F169:F213)</f>
         <v/>
       </c>
       <c r="G214" s="24">
@@ -9491,7 +9514,7 @@
       <c r="C215" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D215" s="17" t="n">
+      <c r="D215" s="49" t="n">
         <v>92.19</v>
       </c>
       <c r="E215" s="18" t="n">
@@ -9531,7 +9554,7 @@
       <c r="C216" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D216" s="17" t="n">
+      <c r="D216" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E216" s="18" t="n">
@@ -9571,7 +9594,7 @@
       <c r="C217" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D217" s="17" t="n">
+      <c r="D217" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E217" s="18" t="n">
@@ -9611,7 +9634,7 @@
       <c r="C218" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D218" s="17" t="n">
+      <c r="D218" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E218" s="18" t="n">
@@ -9651,7 +9674,7 @@
       <c r="C219" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D219" s="17" t="n">
+      <c r="D219" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E219" s="18" t="n">
@@ -9691,7 +9714,7 @@
       <c r="C220" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D220" s="17" t="n">
+      <c r="D220" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E220" s="18" t="n">
@@ -9731,7 +9754,7 @@
       <c r="C221" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D221" s="17" t="n">
+      <c r="D221" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E221" s="18" t="n">
@@ -9771,7 +9794,7 @@
       <c r="C222" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D222" s="17" t="n">
+      <c r="D222" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E222" s="18" t="n">
@@ -9811,7 +9834,7 @@
       <c r="C223" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D223" s="17" t="n">
+      <c r="D223" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E223" s="18" t="n">
@@ -9851,7 +9874,7 @@
       <c r="C224" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D224" s="17" t="n">
+      <c r="D224" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E224" s="18" t="n">
@@ -9891,7 +9914,7 @@
       <c r="C225" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D225" s="17" t="n">
+      <c r="D225" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E225" s="18" t="n">
@@ -9931,7 +9954,7 @@
       <c r="C226" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D226" s="17" t="n">
+      <c r="D226" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E226" s="18" t="n">
@@ -9971,7 +9994,7 @@
       <c r="C227" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D227" s="17" t="n">
+      <c r="D227" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E227" s="18" t="n">
@@ -10011,7 +10034,7 @@
       <c r="C228" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D228" s="17" t="n">
+      <c r="D228" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E228" s="18" t="n">
@@ -10051,7 +10074,7 @@
       <c r="C229" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D229" s="17" t="n">
+      <c r="D229" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E229" s="18" t="n">
@@ -10091,7 +10114,7 @@
       <c r="C230" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D230" s="17" t="n">
+      <c r="D230" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E230" s="18" t="n">
@@ -10131,7 +10154,7 @@
       <c r="C231" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D231" s="17" t="n">
+      <c r="D231" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E231" s="18" t="n">
@@ -10171,7 +10194,7 @@
       <c r="C232" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D232" s="17" t="n">
+      <c r="D232" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E232" s="18" t="n">
@@ -10211,7 +10234,7 @@
       <c r="C233" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D233" s="17" t="n">
+      <c r="D233" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E233" s="18" t="n">
@@ -10251,7 +10274,7 @@
       <c r="C234" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D234" s="17" t="n">
+      <c r="D234" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E234" s="18" t="n">
@@ -10291,7 +10314,7 @@
       <c r="C235" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D235" s="17" t="n">
+      <c r="D235" s="49" t="n">
         <v>88.20999999999999</v>
       </c>
       <c r="E235" s="18" t="n">
@@ -10331,7 +10354,7 @@
       <c r="C236" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D236" s="17" t="n">
+      <c r="D236" s="49" t="n">
         <v>41.13</v>
       </c>
       <c r="E236" s="18" t="n">
@@ -10371,7 +10394,7 @@
       <c r="C237" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D237" s="17" t="n">
+      <c r="D237" s="49" t="n">
         <v>36.86</v>
       </c>
       <c r="E237" s="18" t="n">
@@ -10411,7 +10434,7 @@
       <c r="C238" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D238" s="17" t="n">
+      <c r="D238" s="49" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="E238" s="18" t="n">
@@ -10451,7 +10474,7 @@
       <c r="C239" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D239" s="17" t="n">
+      <c r="D239" s="49" t="n">
         <v>36.95</v>
       </c>
       <c r="E239" s="18" t="n">
@@ -10491,7 +10514,7 @@
       <c r="C240" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D240" s="17" t="n">
+      <c r="D240" s="49" t="n">
         <v>60.84</v>
       </c>
       <c r="E240" s="18" t="n">
@@ -10531,7 +10554,7 @@
       <c r="C241" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D241" s="17" t="n">
+      <c r="D241" s="49" t="n">
         <v>36.74</v>
       </c>
       <c r="E241" s="18" t="n">
@@ -10571,7 +10594,7 @@
       <c r="C242" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D242" s="17" t="n">
+      <c r="D242" s="49" t="n">
         <v>48.57</v>
       </c>
       <c r="E242" s="18" t="n">
@@ -10611,7 +10634,7 @@
       <c r="C243" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D243" s="17" t="n">
+      <c r="D243" s="49" t="n">
         <v>54.34</v>
       </c>
       <c r="E243" s="18" t="n">
@@ -10651,7 +10674,7 @@
       <c r="C244" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D244" s="17" t="n">
+      <c r="D244" s="49" t="n">
         <v>41.69</v>
       </c>
       <c r="E244" s="18" t="n">
@@ -10691,7 +10714,7 @@
       <c r="C245" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D245" s="17" t="n">
+      <c r="D245" s="49" t="n">
         <v>37.01</v>
       </c>
       <c r="E245" s="18" t="n">
@@ -10731,7 +10754,7 @@
       <c r="C246" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D246" s="17" t="n">
+      <c r="D246" s="49" t="n">
         <v>18.5</v>
       </c>
       <c r="E246" s="18" t="n">
@@ -10771,7 +10794,7 @@
       <c r="C247" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D247" s="17" t="n">
+      <c r="D247" s="49" t="n">
         <v>55.07</v>
       </c>
       <c r="E247" s="18" t="n">
@@ -10811,7 +10834,7 @@
       <c r="C248" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D248" s="17" t="n">
+      <c r="D248" s="49" t="n">
         <v>35.17</v>
       </c>
       <c r="E248" s="18" t="n">
@@ -10851,7 +10874,7 @@
       <c r="C249" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D249" s="17" t="n">
+      <c r="D249" s="49" t="n">
         <v>15.99</v>
       </c>
       <c r="E249" s="18" t="n">
@@ -10891,7 +10914,7 @@
       <c r="C250" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D250" s="17" t="n">
+      <c r="D250" s="49" t="n">
         <v>33.26</v>
       </c>
       <c r="E250" s="18" t="n">
@@ -10931,7 +10954,7 @@
       <c r="C251" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D251" s="17" t="n">
+      <c r="D251" s="49" t="n">
         <v>5.85</v>
       </c>
       <c r="E251" s="18" t="n">
@@ -10971,7 +10994,7 @@
       <c r="C252" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D252" s="17" t="n">
+      <c r="D252" s="49" t="n">
         <v>0.98</v>
       </c>
       <c r="E252" s="18" t="n">
@@ -11011,7 +11034,7 @@
       <c r="C253" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D253" s="17" t="n">
+      <c r="D253" s="49" t="n">
         <v>0.36</v>
       </c>
       <c r="E253" s="18" t="n">
@@ -11051,7 +11074,7 @@
       <c r="C254" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D254" s="17" t="n">
+      <c r="D254" s="49" t="n">
         <v>14.09</v>
       </c>
       <c r="E254" s="18" t="n">
@@ -11091,7 +11114,7 @@
       <c r="C255" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D255" s="17" t="n">
+      <c r="D255" s="49" t="n">
         <v>4.68</v>
       </c>
       <c r="E255" s="18" t="n">
@@ -11131,7 +11154,7 @@
       <c r="C256" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D256" s="17" t="n">
+      <c r="D256" s="49" t="n">
         <v>0.36</v>
       </c>
       <c r="E256" s="18" t="n">
@@ -11172,7 +11195,7 @@
         <f>SUM(C215:C256)</f>
         <v/>
       </c>
-      <c r="D257" s="22">
+      <c r="D257" s="50">
         <f>SUM(D215:D256)</f>
         <v/>
       </c>
@@ -11181,7 +11204,7 @@
         <v/>
       </c>
       <c r="F257" s="23">
-        <f>SUM(F215:F256)</f>
+        <f>SUMIF(E215:E256,"&gt;0",F215:F256)</f>
         <v/>
       </c>
       <c r="G257" s="24">
@@ -11219,7 +11242,7 @@
       <c r="C258" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D258" s="17" t="n">
+      <c r="D258" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E258" s="18" t="n">
@@ -11259,7 +11282,7 @@
       <c r="C259" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D259" s="17" t="n">
+      <c r="D259" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E259" s="18" t="n">
@@ -11299,7 +11322,7 @@
       <c r="C260" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D260" s="17" t="n">
+      <c r="D260" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E260" s="18" t="n">
@@ -11339,7 +11362,7 @@
       <c r="C261" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D261" s="17" t="n">
+      <c r="D261" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E261" s="18" t="n">
@@ -11379,7 +11402,7 @@
       <c r="C262" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D262" s="17" t="n">
+      <c r="D262" s="49" t="n">
         <v>90.88</v>
       </c>
       <c r="E262" s="18" t="n">
@@ -11419,7 +11442,7 @@
       <c r="C263" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D263" s="17" t="n">
+      <c r="D263" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E263" s="18" t="n">
@@ -11459,7 +11482,7 @@
       <c r="C264" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D264" s="17" t="n">
+      <c r="D264" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E264" s="18" t="n">
@@ -11499,7 +11522,7 @@
       <c r="C265" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D265" s="17" t="n">
+      <c r="D265" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E265" s="18" t="n">
@@ -11539,7 +11562,7 @@
       <c r="C266" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D266" s="17" t="n">
+      <c r="D266" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E266" s="18" t="n">
@@ -11579,7 +11602,7 @@
       <c r="C267" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D267" s="17" t="n">
+      <c r="D267" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E267" s="18" t="n">
@@ -11619,7 +11642,7 @@
       <c r="C268" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D268" s="17" t="n">
+      <c r="D268" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E268" s="18" t="n">
@@ -11659,7 +11682,7 @@
       <c r="C269" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D269" s="17" t="n">
+      <c r="D269" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E269" s="18" t="n">
@@ -11699,7 +11722,7 @@
       <c r="C270" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D270" s="17" t="n">
+      <c r="D270" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E270" s="18" t="n">
@@ -11739,7 +11762,7 @@
       <c r="C271" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D271" s="17" t="n">
+      <c r="D271" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E271" s="18" t="n">
@@ -11779,7 +11802,7 @@
       <c r="C272" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D272" s="17" t="n">
+      <c r="D272" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E272" s="18" t="n">
@@ -11819,7 +11842,7 @@
       <c r="C273" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D273" s="17" t="n">
+      <c r="D273" s="49" t="n">
         <v>92.92</v>
       </c>
       <c r="E273" s="18" t="n">
@@ -11859,7 +11882,7 @@
       <c r="C274" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D274" s="17" t="n">
+      <c r="D274" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E274" s="18" t="n">
@@ -11899,7 +11922,7 @@
       <c r="C275" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D275" s="17" t="n">
+      <c r="D275" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E275" s="18" t="n">
@@ -11939,7 +11962,7 @@
       <c r="C276" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D276" s="17" t="n">
+      <c r="D276" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E276" s="18" t="n">
@@ -11979,7 +12002,7 @@
       <c r="C277" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D277" s="17" t="n">
+      <c r="D277" s="49" t="n">
         <v>36.99</v>
       </c>
       <c r="E277" s="18" t="n">
@@ -12019,7 +12042,7 @@
       <c r="C278" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D278" s="17" t="n">
+      <c r="D278" s="49" t="n">
         <v>52.18</v>
       </c>
       <c r="E278" s="18" t="n">
@@ -12059,7 +12082,7 @@
       <c r="C279" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D279" s="17" t="n">
+      <c r="D279" s="49" t="n">
         <v>43.51</v>
       </c>
       <c r="E279" s="18" t="n">
@@ -12099,7 +12122,7 @@
       <c r="C280" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D280" s="17" t="n">
+      <c r="D280" s="49" t="n">
         <v>37.13</v>
       </c>
       <c r="E280" s="18" t="n">
@@ -12139,7 +12162,7 @@
       <c r="C281" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D281" s="17" t="n">
+      <c r="D281" s="49" t="n">
         <v>52.09</v>
       </c>
       <c r="E281" s="18" t="n">
@@ -12179,7 +12202,7 @@
       <c r="C282" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D282" s="17" t="n">
+      <c r="D282" s="49" t="n">
         <v>44.74</v>
       </c>
       <c r="E282" s="18" t="n">
@@ -12219,7 +12242,7 @@
       <c r="C283" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D283" s="17" t="n">
+      <c r="D283" s="49" t="n">
         <v>40.28</v>
       </c>
       <c r="E283" s="18" t="n">
@@ -12259,7 +12282,7 @@
       <c r="C284" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D284" s="17" t="n">
+      <c r="D284" s="49" t="n">
         <v>44.74</v>
       </c>
       <c r="E284" s="18" t="n">
@@ -12299,7 +12322,7 @@
       <c r="C285" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D285" s="17" t="n">
+      <c r="D285" s="49" t="n">
         <v>42.49</v>
       </c>
       <c r="E285" s="18" t="n">
@@ -12339,7 +12362,7 @@
       <c r="C286" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D286" s="17" t="n">
+      <c r="D286" s="49" t="n">
         <v>30.71</v>
       </c>
       <c r="E286" s="18" t="n">
@@ -12379,7 +12402,7 @@
       <c r="C287" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D287" s="17" t="n">
+      <c r="D287" s="49" t="n">
         <v>40.38</v>
       </c>
       <c r="E287" s="18" t="n">
@@ -12419,7 +12442,7 @@
       <c r="C288" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D288" s="17" t="n">
+      <c r="D288" s="49" t="n">
         <v>36.8</v>
       </c>
       <c r="E288" s="18" t="n">
@@ -12459,7 +12482,7 @@
       <c r="C289" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D289" s="17" t="n">
+      <c r="D289" s="49" t="n">
         <v>52.36</v>
       </c>
       <c r="E289" s="18" t="n">
@@ -12499,7 +12522,7 @@
       <c r="C290" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D290" s="17" t="n">
+      <c r="D290" s="49" t="n">
         <v>36.79</v>
       </c>
       <c r="E290" s="18" t="n">
@@ -12539,7 +12562,7 @@
       <c r="C291" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D291" s="17" t="n">
+      <c r="D291" s="49" t="n">
         <v>53.9</v>
       </c>
       <c r="E291" s="18" t="n">
@@ -12579,7 +12602,7 @@
       <c r="C292" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D292" s="17" t="n">
+      <c r="D292" s="49" t="n">
         <v>32.29</v>
       </c>
       <c r="E292" s="18" t="n">
@@ -12619,7 +12642,7 @@
       <c r="C293" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D293" s="17" t="n">
+      <c r="D293" s="49" t="n">
         <v>38.35</v>
       </c>
       <c r="E293" s="18" t="n">
@@ -12659,7 +12682,7 @@
       <c r="C294" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D294" s="17" t="n">
+      <c r="D294" s="49" t="n">
         <v>3.37</v>
       </c>
       <c r="E294" s="18" t="n">
@@ -12699,7 +12722,7 @@
       <c r="C295" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D295" s="17" t="n">
+      <c r="D295" s="49" t="n">
         <v>36.94</v>
       </c>
       <c r="E295" s="18" t="n">
@@ -12739,7 +12762,7 @@
       <c r="C296" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D296" s="17" t="n">
+      <c r="D296" s="49" t="n">
         <v>36.9</v>
       </c>
       <c r="E296" s="18" t="n">
@@ -12779,7 +12802,7 @@
       <c r="C297" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D297" s="17" t="n">
+      <c r="D297" s="49" t="n">
         <v>34.97</v>
       </c>
       <c r="E297" s="18" t="n">
@@ -12819,7 +12842,7 @@
       <c r="C298" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D298" s="17" t="n">
+      <c r="D298" s="49" t="n">
         <v>0.62</v>
       </c>
       <c r="E298" s="18" t="n">
@@ -12860,7 +12883,7 @@
         <f>SUM(C258:C298)</f>
         <v/>
       </c>
-      <c r="D299" s="22">
+      <c r="D299" s="50">
         <f>SUM(D258:D298)</f>
         <v/>
       </c>
@@ -12869,7 +12892,7 @@
         <v/>
       </c>
       <c r="F299" s="23">
-        <f>SUM(F258:F298)</f>
+        <f>SUMIF(E258:E298,"&gt;0",F258:F298)</f>
         <v/>
       </c>
       <c r="G299" s="24">
@@ -12904,7 +12927,7 @@
         <f>C46+C91+C130+C168+C214+C257+C299</f>
         <v/>
       </c>
-      <c r="D300" s="27">
+      <c r="D300" s="51">
         <f>D46+D91+D130+D168+D214+D257+D299</f>
         <v/>
       </c>
@@ -12980,7 +13003,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -12988,7 +13010,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -56744,7 +56765,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -76927,7 +76947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -76942,7 +76962,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="44" t="inlineStr">
         <is>
